--- a/data/availability/projects/m-squared-developments/el-masyaf-north-coast.xlsx
+++ b/data/availability/projects/m-squared-developments/el-masyaf-north-coast.xlsx
@@ -461,7 +461,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
         <v>4</v>
@@ -582,17 +582,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Phase 1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>8/5/2028</t>
+          <t>Aug 2028</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
     </row>
@@ -611,19 +611,19 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
         <v>105</v>
       </c>
       <c r="F3" t="n">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="G3" t="n">
         <v>15.71</v>
       </c>
       <c r="H3" t="n">
-        <v>25.52</v>
+        <v>20.81</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -632,17 +632,17 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Lagoon</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>8/5/2029</t>
+          <t>Aug 2029</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
     </row>
@@ -654,26 +654,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Lagoon Chalet</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="F4" t="n">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="G4" t="n">
-        <v>36.68</v>
+        <v>20.87</v>
       </c>
       <c r="H4" t="n">
-        <v>36.68</v>
+        <v>25.52</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -682,17 +682,17 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Lagoon</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>8/5/2029</t>
+          <t>Aug 2029</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
     </row>
@@ -704,45 +704,45 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Chalet</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>118</v>
+        <v>165</v>
       </c>
       <c r="F5" t="n">
-        <v>118</v>
+        <v>165</v>
       </c>
       <c r="G5" t="n">
-        <v>18.2</v>
+        <v>36.68</v>
       </c>
       <c r="H5" t="n">
-        <v>18.2</v>
+        <v>36.68</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Standard Finishing</t>
+          <t>Fully Finished</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Lagoon</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Aug 2029</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
     </row>
@@ -758,41 +758,41 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>160</v>
+        <v>118</v>
       </c>
       <c r="F6" t="n">
-        <v>160</v>
+        <v>118</v>
       </c>
       <c r="G6" t="n">
-        <v>29.9</v>
+        <v>18.2</v>
       </c>
       <c r="H6" t="n">
-        <v>29.9</v>
+        <v>18.2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Standard Finishing</t>
+          <t>Fully Finished</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Phase 2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Aug 2030</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
     </row>
@@ -804,45 +804,195 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>160</v>
+      </c>
+      <c r="F7" t="n">
+        <v>160</v>
+      </c>
+      <c r="G7" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="H7" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Fully Finished</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Phase 2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Aug 2030</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>10% DP over 8 Yrs</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>el-masyaf-north-coast</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>Staggered Chalet</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>75</v>
+      </c>
+      <c r="F8" t="n">
+        <v>75</v>
+      </c>
+      <c r="G8" t="n">
+        <v>15.43</v>
+      </c>
+      <c r="H8" t="n">
+        <v>15.43</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Fully Finished</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Phase 2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Aug 2030</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>10% DP over 8 Yrs</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>el-masyaf-north-coast</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Staggered Chalet</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
         <v>2</v>
       </c>
-      <c r="D7" t="n">
-        <v>7</v>
-      </c>
-      <c r="E7" t="n">
-        <v>75</v>
-      </c>
-      <c r="F7" t="n">
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>90</v>
+      </c>
+      <c r="F9" t="n">
+        <v>110</v>
+      </c>
+      <c r="G9" t="n">
+        <v>17.39</v>
+      </c>
+      <c r="H9" t="n">
+        <v>23.98</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Fully Finished</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Phase 2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Aug 2030</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>10% DP over 8 Yrs</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>el-masyaf-north-coast</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Staggered Chalet</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
         <v>170</v>
       </c>
-      <c r="G7" t="n">
-        <v>15.43</v>
-      </c>
-      <c r="H7" t="n">
+      <c r="F10" t="n">
+        <v>170</v>
+      </c>
+      <c r="G10" t="n">
         <v>33.05</v>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Fully Finished</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Masyaf</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>8/5/2030</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>10% DP over 7-8 yrs</t>
+      <c r="H10" t="n">
+        <v>33.05</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Fully Finished</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Phase 2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Aug 2030</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
     </row>
@@ -945,11 +1095,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Phase 1</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -959,10 +1109,14 @@
       <c r="G2" t="n">
         <v>232</v>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>373.1m Garden</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Scenic View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -970,12 +1124,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>8/5/2028</t>
+          <t>Aug 2028</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1002,11 +1156,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Phase 1</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1016,10 +1170,14 @@
       <c r="G3" t="n">
         <v>232</v>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>255.2m Garden</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Scenic View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -1027,12 +1185,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>8/5/2028</t>
+          <t>Aug 2028</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1059,11 +1217,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Phase 1</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1073,10 +1231,14 @@
       <c r="G4" t="n">
         <v>232</v>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>445.9m Garden</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Scenic View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -1084,12 +1246,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>8/5/2028</t>
+          <t>Aug 2028</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1116,11 +1278,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Phase 1</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1130,10 +1292,14 @@
       <c r="G5" t="n">
         <v>232</v>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>422m Garden</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Scenic View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -1141,12 +1307,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>8/5/2028</t>
+          <t>Aug 2028</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1173,7 +1339,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Lagoon</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1187,10 +1353,14 @@
       <c r="G6" t="n">
         <v>105</v>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>80m Garden · Ground</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Scenic View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -1198,12 +1368,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>8/5/2029</t>
+          <t>Aug 2029</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1230,11 +1400,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Lagoon</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1244,10 +1414,14 @@
       <c r="G7" t="n">
         <v>145</v>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>45m Roof · 2nd &amp; 3rd Floor</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Scenic View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -1255,12 +1429,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>8/5/2029</t>
+          <t>Aug 2029</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1287,11 +1461,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Lagoon</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1301,10 +1475,14 @@
       <c r="G8" t="n">
         <v>165</v>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>208.6m Garden · 35m Roof</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Scenic View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -1312,12 +1490,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>8/5/2029</t>
+          <t>Aug 2029</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1344,11 +1522,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Lagoon</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1358,10 +1536,14 @@
       <c r="G9" t="n">
         <v>145</v>
       </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>45m Roof</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Scenic View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -1369,12 +1551,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>8/5/2029</t>
+          <t>Aug 2029</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1401,7 +1583,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Lagoon</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1415,10 +1597,14 @@
       <c r="G10" t="n">
         <v>105</v>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>80m Garden</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Scenic View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1426,12 +1612,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>8/5/2029</t>
+          <t>Aug 2029</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1458,11 +1644,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Lagoon</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1472,10 +1658,14 @@
       <c r="G11" t="n">
         <v>145</v>
       </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>45m Roof</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Scenic View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1483,12 +1673,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>8/5/2029</t>
+          <t>Aug 2029</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1515,7 +1705,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Lagoon</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1529,10 +1719,14 @@
       <c r="G12" t="n">
         <v>105</v>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>80m Garden</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Scenic View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1540,12 +1734,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>8/5/2029</t>
+          <t>Aug 2029</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1572,7 +1766,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Lagoon</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1586,10 +1780,14 @@
       <c r="G13" t="n">
         <v>105</v>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>80m Garden</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Scenic View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1597,12 +1795,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>8/5/2029</t>
+          <t>Aug 2029</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1629,11 +1827,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Lagoon</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1643,10 +1841,14 @@
       <c r="G14" t="n">
         <v>145</v>
       </c>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>45m Roof</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Scenic View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1654,12 +1856,12 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>8/5/2029</t>
+          <t>Aug 2029</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1686,7 +1888,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Lagoon</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1700,10 +1902,14 @@
       <c r="G15" t="n">
         <v>110</v>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1st Floor</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Scenic View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -1711,12 +1917,12 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>8/5/2029</t>
+          <t>Aug 2029</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1743,7 +1949,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Lagoon</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1760,7 +1966,7 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Scenic View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1768,12 +1974,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>8/5/2029</t>
+          <t>Aug 2029</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1800,7 +2006,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Lagoon</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1814,10 +2020,14 @@
       <c r="G17" t="n">
         <v>105</v>
       </c>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>80m Garden</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Scenic View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -1825,12 +2035,12 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>8/5/2029</t>
+          <t>Aug 2029</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1857,11 +2067,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Lagoon</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1871,10 +2081,14 @@
       <c r="G18" t="n">
         <v>145</v>
       </c>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>45m Roof</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Scenic View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -1882,12 +2096,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>8/5/2029</t>
+          <t>Aug 2029</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1914,7 +2128,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Phase 2</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1922,16 +2136,20 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Standard Finishing</t>
+          <t>Fully Finished</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>118</v>
       </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2nd Floor</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Scenic View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -1939,12 +2157,12 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Aug 2030</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1971,7 +2189,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Phase 2</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1979,16 +2197,20 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Standard Finishing</t>
+          <t>Fully Finished</t>
         </is>
       </c>
       <c r="G20" t="n">
         <v>160</v>
       </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>75m Roof</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Scenic View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -1996,12 +2218,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Aug 2030</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2028,11 +2250,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Phase 2</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2042,10 +2264,14 @@
       <c r="G21" t="n">
         <v>75</v>
       </c>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>50m Garden</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Scenic View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -2053,12 +2279,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Aug 2030</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2085,7 +2311,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Phase 2</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2099,10 +2325,14 @@
       <c r="G22" t="n">
         <v>90</v>
       </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>40m Garden</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Scenic View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -2110,12 +2340,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Aug 2030</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2142,7 +2372,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Phase 2</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2156,10 +2386,14 @@
       <c r="G23" t="n">
         <v>110</v>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>65m Garden</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Scenic View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -2167,12 +2401,12 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Aug 2030</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2199,7 +2433,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Phase 2</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2213,10 +2447,14 @@
       <c r="G24" t="n">
         <v>110</v>
       </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>65m Garden</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Scenic View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -2224,12 +2462,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Aug 2030</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2256,7 +2494,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Phase 2</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -2270,10 +2508,14 @@
       <c r="G25" t="n">
         <v>90</v>
       </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>40m Garden</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Scenic View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -2281,12 +2523,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Aug 2030</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2313,7 +2555,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Phase 2</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -2327,10 +2569,14 @@
       <c r="G26" t="n">
         <v>105</v>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>100m Garden</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Scenic View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -2338,12 +2584,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Aug 2030</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2370,11 +2616,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Phase 2</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2384,10 +2630,14 @@
       <c r="G27" t="n">
         <v>170</v>
       </c>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2nd Floor</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Scenic View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -2395,12 +2645,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Aug 2030</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2427,7 +2677,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Lagoon</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -2441,10 +2691,14 @@
       <c r="G28" t="n">
         <v>105</v>
       </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>80m Garden</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Scenic View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -2452,12 +2706,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>8/5/2029</t>
+          <t>Aug 2029</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2484,7 +2738,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Lagoon</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -2501,7 +2755,7 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Scenic View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -2509,12 +2763,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>8/5/2029</t>
+          <t>Aug 2029</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2541,7 +2795,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Lagoon</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -2558,7 +2812,7 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Scenic View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -2566,12 +2820,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>8/5/2029</t>
+          <t>Aug 2029</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2598,7 +2852,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Lagoon</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -2615,7 +2869,7 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Scenic View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -2623,12 +2877,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>8/5/2029</t>
+          <t>Aug 2029</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2655,11 +2909,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Lagoon</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2669,10 +2923,14 @@
       <c r="G32" t="n">
         <v>145</v>
       </c>
-      <c r="H32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>45m Roof</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Scenic View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J32" t="n">
@@ -2680,12 +2938,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>8/5/2029</t>
+          <t>Aug 2029</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2712,11 +2970,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Lagoon</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2726,10 +2984,14 @@
       <c r="G33" t="n">
         <v>145</v>
       </c>
-      <c r="H33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>45m Roof</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Scenic View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J33" t="n">
@@ -2737,12 +2999,12 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>8/5/2029</t>
+          <t>Aug 2029</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2769,7 +3031,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Lagoon</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -2786,7 +3048,7 @@
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Scenic View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J34" t="n">
@@ -2794,12 +3056,12 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>8/5/2029</t>
+          <t>Aug 2029</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2826,7 +3088,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Lagoon</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -2843,7 +3105,7 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Scenic View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J35" t="n">
@@ -2851,12 +3113,12 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>8/5/2029</t>
+          <t>Aug 2029</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2883,11 +3145,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Lagoon</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2897,10 +3159,14 @@
       <c r="G36" t="n">
         <v>145</v>
       </c>
-      <c r="H36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>45m Roof</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Scenic View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J36" t="n">
@@ -2908,12 +3174,12 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>8/5/2029</t>
+          <t>Aug 2029</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2940,7 +3206,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Lagoon</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -2957,7 +3223,7 @@
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Scenic View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J37" t="n">
@@ -2965,12 +3231,12 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>8/5/2029</t>
+          <t>Aug 2029</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2997,7 +3263,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Lagoon</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -3014,7 +3280,7 @@
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Scenic View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J38" t="n">
@@ -3022,12 +3288,12 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>8/5/2029</t>
+          <t>Aug 2029</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3054,11 +3320,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Lagoon</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3068,10 +3334,14 @@
       <c r="G39" t="n">
         <v>145</v>
       </c>
-      <c r="H39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>45m Roof</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Scenic View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J39" t="n">
@@ -3079,12 +3349,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>8/5/2029</t>
+          <t>Aug 2029</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3111,11 +3381,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Masyaf</t>
+          <t>Lagoon</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3125,10 +3395,14 @@
       <c r="G40" t="n">
         <v>145</v>
       </c>
-      <c r="H40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>45m Roof</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Scenic View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J40" t="n">
@@ -3136,12 +3410,12 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>8/5/2029</t>
+          <t>Aug 2029</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>10% DP over 7-8 yrs</t>
+          <t>10% DP over 8 Yrs</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">

--- a/data/availability/projects/m-squared-developments/el-masyaf-north-coast.xlsx
+++ b/data/availability/projects/m-squared-developments/el-masyaf-north-coast.xlsx
@@ -854,7 +854,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Staggered Chalet</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -904,7 +904,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Staggered Chalet</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Staggered Chalet</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1963,7 +1963,6 @@
       <c r="G16" t="n">
         <v>120</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2240,7 +2239,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Staggered Chalet</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2301,7 +2300,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Staggered Chalet</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2362,7 +2361,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Staggered Chalet</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2423,7 +2422,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Staggered Chalet</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2484,7 +2483,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Staggered Chalet</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2545,7 +2544,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Staggered Chalet</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2606,7 +2605,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Staggered Chalet</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2752,7 +2751,6 @@
       <c r="G29" t="n">
         <v>110</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2809,7 +2807,6 @@
       <c r="G30" t="n">
         <v>110</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2866,7 +2863,6 @@
       <c r="G31" t="n">
         <v>110</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3045,7 +3041,6 @@
       <c r="G34" t="n">
         <v>110</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3102,7 +3097,6 @@
       <c r="G35" t="n">
         <v>110</v>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3220,7 +3214,6 @@
       <c r="G37" t="n">
         <v>110</v>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3277,7 +3270,6 @@
       <c r="G38" t="n">
         <v>110</v>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>Landscape</t>
